--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.9053528718121</v>
+        <v>2.747119841669466</v>
       </c>
       <c r="D2" t="n">
-        <v>15.07053989783856</v>
+        <v>2.448962733398766</v>
       </c>
       <c r="E2" t="n">
-        <v>14.47685260228375</v>
+        <v>2.35248854787111</v>
       </c>
       <c r="F2" t="n">
-        <v>9.068749736169901</v>
+        <v>1.473671832127609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.78364478359858</v>
+        <v>5.81484227733477</v>
       </c>
       <c r="D3" t="n">
-        <v>37.58152013360009</v>
+        <v>6.106997021710014</v>
       </c>
       <c r="E3" t="n">
-        <v>14.47685260228375</v>
+        <v>2.35248854787111</v>
       </c>
       <c r="F3" t="n">
-        <v>9.068749736169901</v>
+        <v>1.473671832127609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.52799855861502</v>
+        <v>6.09829976577494</v>
       </c>
       <c r="D4" t="n">
-        <v>37.86688680174726</v>
+        <v>6.153369105283931</v>
       </c>
       <c r="E4" t="n">
-        <v>14.47685260228375</v>
+        <v>2.35248854787111</v>
       </c>
       <c r="F4" t="n">
-        <v>9.068749736169901</v>
+        <v>1.473671832127609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.732954134421373</v>
+        <v>0.6066050468434731</v>
       </c>
       <c r="D5" t="n">
-        <v>31.57908744534411</v>
+        <v>5.131601709868417</v>
       </c>
       <c r="E5" t="n">
-        <v>14.47685260228375</v>
+        <v>2.35248854787111</v>
       </c>
       <c r="F5" t="n">
-        <v>9.068749736169901</v>
+        <v>1.473671832127609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.72202853471362</v>
+        <v>6.779829636890963</v>
       </c>
       <c r="D6" t="n">
-        <v>39.71430551074588</v>
+        <v>6.453574645496206</v>
       </c>
       <c r="E6" t="n">
-        <v>14.47685260228375</v>
+        <v>2.35248854787111</v>
       </c>
       <c r="F6" t="n">
-        <v>9.068749736169901</v>
+        <v>1.473671832127609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
